--- a/cypress/Excels/Negative/Adding address/Address Label.xlsx
+++ b/cypress/Excels/Negative/Adding address/Address Label.xlsx
@@ -76,7 +76,7 @@
     <t>playstoretest@pococare.com</t>
   </si>
   <si>
-    <t>test1</t>
+    <t>test</t>
   </si>
 </sst>
 </file>
